--- a/artfynd/A 6583-2024 artfynd.xlsx
+++ b/artfynd/A 6583-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121492748</v>
       </c>
       <c r="B2" t="n">
-        <v>97055</v>
+        <v>97058</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 6583-2024 artfynd.xlsx
+++ b/artfynd/A 6583-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121492748</v>
       </c>
       <c r="B2" t="n">
-        <v>97058</v>
+        <v>97064</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 6583-2024 artfynd.xlsx
+++ b/artfynd/A 6583-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121492748</v>
       </c>
       <c r="B2" t="n">
-        <v>97064</v>
+        <v>97065</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 6583-2024 artfynd.xlsx
+++ b/artfynd/A 6583-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121492748</v>
       </c>
       <c r="B2" t="n">
-        <v>97065</v>
+        <v>97073</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
